--- a/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444666370446814</v>
       </c>
       <c r="C2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>27678977</v>
+        <v>4276463</v>
       </c>
       <c r="L2" t="n">
-        <v>15996664</v>
+        <v>2174700</v>
       </c>
       <c r="M2" t="n">
-        <v>4063339</v>
+        <v>498991</v>
       </c>
       <c r="N2" t="n">
-        <v>233635</v>
+        <v>18699</v>
       </c>
       <c r="O2" t="n">
-        <v>2414108</v>
+        <v>305083</v>
       </c>
       <c r="P2" t="n">
-        <v>949343</v>
+        <v>120825</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999690651893616</v>
+        <v>0.9999295473098755</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9020094871520996</v>
+        <v>0.8221445679664612</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8078607320785522</v>
+        <v>0.6669113636016846</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7601219415664673</v>
+        <v>0.5799644589424133</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5019000768661499</v>
+        <v>0.1836692541837692</v>
       </c>
       <c r="V2" t="n">
-        <v>0.799199104309082</v>
+        <v>0.6317569017410278</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8649482727050781</v>
+        <v>0.7475730776786804</v>
       </c>
       <c r="X2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="AG2" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AH2" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AI2" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.95653235912323</v>
+        <v>0.9562515616416931</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911312997341156</v>
+        <v>0.9114683270454407</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580047488212585</v>
+        <v>0.8577601909637451</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.66214919090271</v>
+        <v>0.6615037322044373</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646644592285</v>
+        <v>0.9018846154212952</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024449655927808</v>
       </c>
       <c r="C3" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>27678977</v>
+        <v>4276463</v>
       </c>
       <c r="E3" t="n">
-        <v>2624716</v>
+        <v>747535</v>
       </c>
       <c r="F3" t="n">
-        <v>50171</v>
+        <v>18126</v>
       </c>
       <c r="G3" t="n">
-        <v>6047</v>
+        <v>1936</v>
       </c>
       <c r="H3" t="n">
-        <v>3262</v>
+        <v>1388</v>
       </c>
       <c r="I3" t="n">
-        <v>314</v>
+        <v>106</v>
       </c>
       <c r="J3" t="n">
-        <v>60416542</v>
+        <v>10069173</v>
       </c>
       <c r="K3" t="n">
-        <v>65125522</v>
+        <v>10445288</v>
       </c>
       <c r="L3" t="n">
-        <v>74996645</v>
+        <v>12034637</v>
       </c>
       <c r="M3" t="n">
-        <v>91607239</v>
+        <v>15118718</v>
       </c>
       <c r="N3" t="n">
-        <v>97728050</v>
+        <v>16243387</v>
       </c>
       <c r="O3" t="n">
-        <v>94832602</v>
+        <v>15728176</v>
       </c>
       <c r="P3" t="n">
-        <v>97187746</v>
+        <v>16181762</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9115856885910034</v>
+        <v>0.8475661873817444</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8122296333312988</v>
+        <v>0.6599579453468323</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7247602939605713</v>
+        <v>0.5331721305847168</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4358178973197937</v>
+        <v>0.208918035030365</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7897379398345947</v>
+        <v>0.5982078313827515</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8183814883232117</v>
+        <v>0.6246122717857361</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="Z3" t="n">
-        <v>1194510</v>
+        <v>199161</v>
       </c>
       <c r="AA3" t="n">
-        <v>51498</v>
+        <v>8614</v>
       </c>
       <c r="AB3" t="n">
-        <v>40960</v>
+        <v>6858</v>
       </c>
       <c r="AC3" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60417720</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>66811145</v>
+        <v>11149408</v>
       </c>
       <c r="AG3" t="n">
-        <v>77057112</v>
+        <v>12829512</v>
       </c>
       <c r="AH3" t="n">
-        <v>92093936</v>
+        <v>15347098</v>
       </c>
       <c r="AI3" t="n">
-        <v>97778931</v>
+        <v>16296228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95139602</v>
+        <v>15855995</v>
       </c>
       <c r="AK3" t="n">
-        <v>97256450</v>
+        <v>16209305</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575998783111572</v>
+        <v>0.9574463367462158</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099897742271423</v>
+        <v>0.9100549221038818</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574815392494202</v>
+        <v>0.8570517301559448</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616687178611755</v>
+        <v>0.6608754992485046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015793204307556</v>
+        <v>0.901373565196991</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319545241795172</v>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>2841157</v>
+        <v>871272</v>
       </c>
       <c r="E4" t="n">
-        <v>15996664</v>
+        <v>2174700</v>
       </c>
       <c r="F4" t="n">
-        <v>761768</v>
+        <v>212057</v>
       </c>
       <c r="G4" t="n">
-        <v>29949</v>
+        <v>11934</v>
       </c>
       <c r="H4" t="n">
-        <v>60239</v>
+        <v>23062</v>
       </c>
       <c r="I4" t="n">
-        <v>4940</v>
+        <v>2167</v>
       </c>
       <c r="J4" t="n">
-        <v>1178</v>
+        <v>447</v>
       </c>
       <c r="K4" t="n">
-        <v>3006928</v>
+        <v>925132</v>
       </c>
       <c r="L4" t="n">
-        <v>3804600</v>
+        <v>1086153</v>
       </c>
       <c r="M4" t="n">
-        <v>1282302</v>
+        <v>361391</v>
       </c>
       <c r="N4" t="n">
-        <v>231866</v>
+        <v>83109</v>
       </c>
       <c r="O4" t="n">
-        <v>606551</v>
+        <v>177829</v>
       </c>
       <c r="P4" t="n">
-        <v>148229</v>
+        <v>40798</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999845623970032</v>
+        <v>0.9999647736549377</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9067723155021667</v>
+        <v>0.8346618413925171</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8100392818450928</v>
+        <v>0.6634164452552795</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7420200109481812</v>
+        <v>0.5555848479270935</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4665305316448212</v>
+        <v>0.1954817175865173</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7944403886795044</v>
+        <v>0.6145248413085938</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8410207629203796</v>
+        <v>0.6805834770202637</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1233664</v>
+        <v>206326</v>
       </c>
       <c r="Z4" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AA4" t="n">
-        <v>498690</v>
+        <v>83312</v>
       </c>
       <c r="AB4" t="n">
-        <v>33091</v>
+        <v>5534</v>
       </c>
       <c r="AC4" t="n">
-        <v>6876</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1321305</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1744133</v>
+        <v>291278</v>
       </c>
       <c r="AH4" t="n">
-        <v>795605</v>
+        <v>133011</v>
       </c>
       <c r="AI4" t="n">
-        <v>180985</v>
+        <v>30268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299551</v>
+        <v>50010</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570658206939697</v>
+        <v>0.9568485021591187</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910650908946991</v>
+        <v>0.9107611179351807</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577430844306946</v>
+        <v>0.8574058413505554</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619088649749756</v>
+        <v>0.6611894369125366</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017719030380249</v>
+        <v>0.9016289710998535</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
-        <v>107903</v>
+        <v>37447</v>
       </c>
       <c r="E5" t="n">
-        <v>1017689</v>
+        <v>282068</v>
       </c>
       <c r="F5" t="n">
-        <v>4063339</v>
+        <v>498991</v>
       </c>
       <c r="G5" t="n">
-        <v>88027</v>
+        <v>27023</v>
       </c>
       <c r="H5" t="n">
-        <v>305952</v>
+        <v>81630</v>
       </c>
       <c r="I5" t="n">
-        <v>23446</v>
+        <v>8670</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2684573</v>
+        <v>769117</v>
       </c>
       <c r="L5" t="n">
-        <v>3698091</v>
+        <v>1120510</v>
       </c>
       <c r="M5" t="n">
-        <v>1543120</v>
+        <v>436900</v>
       </c>
       <c r="N5" t="n">
-        <v>302449</v>
+        <v>70805</v>
       </c>
       <c r="O5" t="n">
-        <v>642739</v>
+        <v>204912</v>
       </c>
       <c r="P5" t="n">
-        <v>210682</v>
+        <v>72615</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999880194664001</v>
+        <v>0.9999727606773376</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9422159194946289</v>
+        <v>0.8967928290367126</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9238274693489075</v>
+        <v>0.8655785322189331</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9713143706321716</v>
+        <v>0.9513711333274841</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9945752620697021</v>
+        <v>0.9906241297721863</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9873163104057312</v>
+        <v>0.9766848683357239</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9963560700416565</v>
+        <v>0.9930912852287292</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48367</v>
+        <v>8102</v>
       </c>
       <c r="Z5" t="n">
-        <v>512041</v>
+        <v>85827</v>
       </c>
       <c r="AA5" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AB5" t="n">
-        <v>59802</v>
+        <v>9994</v>
       </c>
       <c r="AC5" t="n">
-        <v>175016</v>
+        <v>29228</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1287418</v>
+        <v>214708</v>
       </c>
       <c r="AG5" t="n">
-        <v>1772729</v>
+        <v>296388</v>
       </c>
       <c r="AH5" t="n">
-        <v>799024</v>
+        <v>133784</v>
       </c>
       <c r="AI5" t="n">
-        <v>181374</v>
+        <v>30353</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300857</v>
+        <v>50299</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735144376754761</v>
+        <v>0.9734575748443604</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642943739891052</v>
+        <v>0.9642016291618347</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838101863861084</v>
+        <v>0.9837478399276733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210821151733</v>
+        <v>0.9963071942329407</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939042329788208</v>
+        <v>0.9938895702362061</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983834028244019</v>
+        <v>0.9983822703361511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>56125</v>
+        <v>15115</v>
       </c>
       <c r="E6" t="n">
-        <v>82393</v>
+        <v>20571</v>
       </c>
       <c r="F6" t="n">
-        <v>106685</v>
+        <v>23064</v>
       </c>
       <c r="G6" t="n">
-        <v>233635</v>
+        <v>18699</v>
       </c>
       <c r="H6" t="n">
-        <v>51967</v>
+        <v>10659</v>
       </c>
       <c r="I6" t="n">
-        <v>5090</v>
+        <v>1346</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38939</v>
+        <v>6528</v>
       </c>
       <c r="Z6" t="n">
-        <v>32230</v>
+        <v>5399</v>
       </c>
       <c r="AA6" t="n">
-        <v>65403</v>
+        <v>10952</v>
       </c>
       <c r="AB6" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AC6" t="n">
-        <v>41916</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>367</v>
+        <v>225</v>
       </c>
       <c r="D7" t="n">
-        <v>1633</v>
+        <v>1265</v>
       </c>
       <c r="E7" t="n">
-        <v>75355</v>
+        <v>33659</v>
       </c>
       <c r="F7" t="n">
-        <v>349129</v>
+        <v>101925</v>
       </c>
       <c r="G7" t="n">
-        <v>101816</v>
+        <v>39329</v>
       </c>
       <c r="H7" t="n">
-        <v>2414108</v>
+        <v>305083</v>
       </c>
       <c r="I7" t="n">
-        <v>114439</v>
+        <v>28509</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4866</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>178032</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45539</v>
+        <v>7616</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>418</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>4447</v>
+        <v>2320</v>
       </c>
       <c r="F8" t="n">
-        <v>14549</v>
+        <v>6219</v>
       </c>
       <c r="G8" t="n">
-        <v>6027</v>
+        <v>2887</v>
       </c>
       <c r="H8" t="n">
-        <v>185131</v>
+        <v>61090</v>
       </c>
       <c r="I8" t="n">
-        <v>949343</v>
+        <v>120825</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
